--- a/tests/Tox-To-MDI-HanSolo.xlsx
+++ b/tests/Tox-To-MDI-HanSolo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD7D378-42D5-9547-AC82-579FF424F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12311E81-68E6-B44D-8BB1-686F81A43A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="1980" windowWidth="30240" windowHeight="17720" xr2:uid="{E8544DCA-7A15-AA41-9C58-6AD37A29F235}"/>
+    <workbookView xWindow="7280" yWindow="9540" windowWidth="30240" windowHeight="17720" xr2:uid="{E8544DCA-7A15-AA41-9C58-6AD37A29F235}"/>
   </bookViews>
   <sheets>
     <sheet name="Han Solo" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="99">
   <si>
     <t>Toxicology-To-MDI Template</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Laboratory Case Number</t>
   </si>
   <si>
-    <t>25-00001</t>
-  </si>
-  <si>
     <t>Performer</t>
   </si>
   <si>
@@ -316,7 +313,25 @@
     <t>SS</t>
   </si>
   <si>
-    <t>123-45-4321</t>
+    <t>Lab Report Code</t>
+  </si>
+  <si>
+    <t>fentaNYL and Norfentanyl panel - Specimen</t>
+  </si>
+  <si>
+    <t>Performer ID System</t>
+  </si>
+  <si>
+    <t>Performer ID</t>
+  </si>
+  <si>
+    <t>urn:mdi:raven:performer</t>
+  </si>
+  <si>
+    <t>2401-001</t>
+  </si>
+  <si>
+    <t>123-45-6789</t>
   </si>
 </sst>
 </file>
@@ -485,7 +500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -514,6 +529,21 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -523,25 +553,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -857,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA2219E-2D71-C14E-8DCA-8D5B763E483A}">
-  <dimension ref="A1:K1048571"/>
+  <dimension ref="A1:K1048574"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
@@ -875,10 +893,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -889,54 +907,54 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:11" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-    </row>
-    <row r="3" spans="1:11" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+    </row>
+    <row r="3" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
@@ -956,11 +974,11 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>9</v>
+      <c r="A6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -974,10 +992,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -991,7 +1009,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1005,10 +1026,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1022,10 +1040,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="9">
-        <v>32608</v>
+        <v>13</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -1039,10 +1057,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="B11" s="9">
+        <v>32608</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1056,10 +1074,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -1071,27 +1089,29 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>22</v>
+      <c r="A14" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>96</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1104,11 +1124,11 @@
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>24</v>
+      <c r="A15" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="1">
+        <v>65748</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -1120,29 +1140,27 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+    <row r="16" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
-        <v>90</v>
+      <c r="A17" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1155,11 +1173,11 @@
       <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
-        <v>91</v>
+      <c r="A18" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -1173,10 +1191,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1189,13 +1207,15 @@
       <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -1204,10 +1224,12 @@
       <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="9"/>
+      <c r="A21" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -1220,10 +1242,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1237,14 +1259,14 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="B23" s="12">
+        <v>28561</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -1254,27 +1276,25 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
+      <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -1283,142 +1303,124 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="3"/>
+      <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="8"/>
-    </row>
-    <row r="27" spans="1:11" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="F27" s="25" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="J27" s="29"/>
-      <c r="K27" s="31"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
-        <v>48</v>
+      <c r="A28" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="15"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="15" t="s">
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="15"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="15"/>
+      <c r="G30" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="21"/>
+      <c r="K30" s="22"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="9"/>
+        <v>47</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="2"/>
@@ -1428,20 +1430,20 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G32" s="15"/>
       <c r="H32" s="2"/>
@@ -1451,136 +1453,148 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="G33" s="15"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="8"/>
-    </row>
-    <row r="35" spans="1:11" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="G35" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="25"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="15"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="15"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>72</v>
+      <c r="A36" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="C36" s="9"/>
       <c r="D36" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="3"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="2"/>
+    <row r="37" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="8"/>
+    </row>
+    <row r="38" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="17"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3"/>
@@ -1592,14 +1606,14 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="3"/>
@@ -1611,14 +1625,14 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="3"/>
@@ -1630,14 +1644,14 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="3"/>
@@ -1649,14 +1663,14 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3"/>
@@ -1668,14 +1682,14 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3"/>
@@ -1687,14 +1701,14 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3"/>
@@ -1706,14 +1720,14 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="3"/>
@@ -1725,13 +1739,15 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="D47" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="E47" s="2"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -1742,16 +1758,14 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>84</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="3"/>
@@ -1761,78 +1775,135 @@
       <c r="J48" s="3"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="8" t="s">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="8"/>
+    </row>
+    <row r="53" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4"/>
+      <c r="B53" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="8"/>
-    </row>
-    <row r="50" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="4"/>
-      <c r="B50" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="21"/>
-    </row>
-    <row r="51" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="18"/>
-    </row>
-    <row r="52" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="18"/>
-    </row>
-    <row r="1048571" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H1048571" s="2"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="28"/>
+      <c r="K53" s="28"/>
+    </row>
+    <row r="54" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="3"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="27"/>
+    </row>
+    <row r="55" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="26"/>
+      <c r="K55" s="27"/>
+    </row>
+    <row r="1048574" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H1048574" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B55:K55"/>
+    <mergeCell ref="B53:K53"/>
+    <mergeCell ref="B54:K54"/>
+    <mergeCell ref="B3:K3"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="B52:K52"/>
-    <mergeCell ref="B50:K50"/>
-    <mergeCell ref="B51:K51"/>
-    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/tests/Tox-To-MDI-HanSolo.xlsx
+++ b/tests/Tox-To-MDI-HanSolo.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc142/Documents/workspace/mortality-reporting/mdi-import/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12311E81-68E6-B44D-8BB1-686F81A43A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1593910F-33E0-EE44-B1D2-DF9B989D73C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7280" yWindow="9540" windowWidth="30240" windowHeight="17720" xr2:uid="{E8544DCA-7A15-AA41-9C58-6AD37A29F235}"/>
+    <workbookView xWindow="4320" yWindow="3600" windowWidth="30240" windowHeight="17720" xr2:uid="{E8544DCA-7A15-AA41-9C58-6AD37A29F235}"/>
   </bookViews>
   <sheets>
-    <sheet name="Han Solo" sheetId="2" r:id="rId1"/>
+    <sheet name="ToxToMDI" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -544,6 +544,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -556,9 +558,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -893,10 +893,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="26"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -928,24 +928,24 @@
       <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="31"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -1124,10 +1124,10 @@
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>65748</v>
       </c>
       <c r="C15" s="9"/>
@@ -1141,10 +1141,10 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="31"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -1358,7 +1358,7 @@
       <c r="K28" s="2"/>
     </row>
     <row r="29" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="31" t="s">
         <v>38</v>
       </c>
       <c r="B29" s="32"/>
@@ -1544,7 +1544,7 @@
       <c r="K36" s="2"/>
     </row>
     <row r="37" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="31" t="s">
         <v>65</v>
       </c>
       <c r="B37" s="32"/>
@@ -1851,57 +1851,53 @@
     </row>
     <row r="53" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
     </row>
     <row r="54" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="27"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="29"/>
     </row>
     <row r="55" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="27"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="29"/>
     </row>
     <row r="1048574" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H1048574" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="5">
     <mergeCell ref="B55:K55"/>
     <mergeCell ref="B53:K53"/>
     <mergeCell ref="B54:K54"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A37:G37"/>
   </mergeCells>
